--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4699,9 +4699,14 @@
       <c r="E125" s="7" t="n">
         <v>46278.6875</v>
       </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F125" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2160664478198272</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4732,9 +4732,14 @@
       <c r="E126" s="7" t="n">
         <v>46278.91666666666</v>
       </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F126" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>1797843087928207</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4765,9 +4765,14 @@
       <c r="E127" s="7" t="n">
         <v>46279.02083333334</v>
       </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F127" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>1048311904689896</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4798,9 +4798,14 @@
       <c r="E128" s="7" t="n">
         <v>46279.6875</v>
       </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F128" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>1366407625274799</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4831,9 +4831,14 @@
       <c r="E129" s="7" t="n">
         <v>46279.91666666666</v>
       </c>
-      <c r="F129" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F129" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>4607503109480677</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4864,9 +4864,14 @@
       <c r="E130" s="7" t="n">
         <v>46280.02083333334</v>
       </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F130" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>2189067671951876</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4897,9 +4897,14 @@
       <c r="E131" s="7" t="n">
         <v>46280.6875</v>
       </c>
-      <c r="F131" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F131" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>1413873874241765</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4930,9 +4930,14 @@
       <c r="E132" s="7" t="n">
         <v>46280.91666666666</v>
       </c>
-      <c r="F132" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F132" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>1842287113805738</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4963,9 +4963,14 @@
       <c r="E133" s="7" t="n">
         <v>46281.02083333334</v>
       </c>
-      <c r="F133" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F133" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>1416341370631838</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4996,9 +4996,14 @@
       <c r="E134" s="7" t="n">
         <v>46281.6875</v>
       </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F134" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>1802052001107903</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5029,9 +5029,14 @@
       <c r="E135" s="7" t="n">
         <v>46281.91666666666</v>
       </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F135" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>2053055965411641</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5062,9 +5062,14 @@
       <c r="E136" s="7" t="n">
         <v>46282.02083333334</v>
       </c>
-      <c r="F136" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F136" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>1648160356913408</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5095,9 +5095,14 @@
       <c r="E137" s="7" t="n">
         <v>46282.6875</v>
       </c>
-      <c r="F137" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F137" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>1109276678215090</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5128,9 +5128,14 @@
       <c r="E138" s="7" t="n">
         <v>46282.91666666666</v>
       </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F138" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>1527535052728826</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5161,9 +5161,14 @@
       <c r="E139" s="7" t="n">
         <v>46283.02083333334</v>
       </c>
-      <c r="F139" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F139" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2719486578470235</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5194,9 +5194,14 @@
       <c r="E140" s="7" t="n">
         <v>46283.6875</v>
       </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F140" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>1103998635401720</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5227,9 +5227,14 @@
       <c r="E141" s="7" t="n">
         <v>46283.91666666666</v>
       </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F141" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>1573458093775807</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5260,9 +5260,14 @@
       <c r="E142" s="7" t="n">
         <v>46284.02083333334</v>
       </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F142" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>2048163215875712</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5293,9 +5293,14 @@
       <c r="E143" s="7" t="n">
         <v>46284.6875</v>
       </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F143" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>1382815636843200</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5326,9 +5326,14 @@
       <c r="E144" s="7" t="n">
         <v>46284.91666666666</v>
       </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F144" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>1401271868162956</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5359,9 +5359,14 @@
       <c r="E145" s="7" t="n">
         <v>46285.02083333334</v>
       </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F145" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>1400044741643644</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5392,9 +5392,14 @@
       <c r="E146" s="7" t="n">
         <v>46285.6875</v>
       </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F146" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>1388901043226658</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5425,9 +5425,14 @@
       <c r="E147" s="7" t="n">
         <v>46285.91666666666</v>
       </c>
-      <c r="F147" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F147" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>1501190825123344</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5458,9 +5458,14 @@
       <c r="E148" s="7" t="n">
         <v>46286.02083333334</v>
       </c>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F148" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>941462371846998</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5491,9 +5491,14 @@
       <c r="E149" s="7" t="n">
         <v>46286.6875</v>
       </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F149" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>1622808522910414</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5524,9 +5524,14 @@
       <c r="E150" s="7" t="n">
         <v>46286.91666666666</v>
       </c>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F150" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>2252317862276501</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5557,9 +5557,14 @@
       <c r="E151" s="7" t="n">
         <v>46287.02083333334</v>
       </c>
-      <c r="F151" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F151" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>1572785934599344</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5590,9 +5590,14 @@
       <c r="E152" s="7" t="n">
         <v>46287.6875</v>
       </c>
-      <c r="F152" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F152" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>1671569044338419</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5623,9 +5623,14 @@
       <c r="E153" s="7" t="n">
         <v>46287.91666666666</v>
       </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F153" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>1091354593815551</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5656,9 +5656,14 @@
       <c r="E154" s="7" t="n">
         <v>46288.02083333334</v>
       </c>
-      <c r="F154" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F154" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>3240146619514232</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5689,9 +5689,14 @@
       <c r="E155" s="7" t="n">
         <v>46288.6875</v>
       </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F155" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>1565756281402265</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5722,9 +5722,14 @@
       <c r="E156" s="7" t="n">
         <v>46288.91666666666</v>
       </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F156" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>1787377716049722</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5755,9 +5755,14 @@
       <c r="E157" s="7" t="n">
         <v>46289.02083333334</v>
       </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F157" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>1595190455717231</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5788,9 +5788,14 @@
       <c r="E158" s="7" t="n">
         <v>46289.6875</v>
       </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F158" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>1628531912002115</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5821,9 +5821,14 @@
       <c r="E159" s="7" t="n">
         <v>46289.91666666666</v>
       </c>
-      <c r="F159" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F159" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>1462828369083798</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5854,9 +5854,14 @@
       <c r="E160" s="7" t="n">
         <v>46290.02083333334</v>
       </c>
-      <c r="F160" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F160" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>1466220968747371</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5887,9 +5887,14 @@
       <c r="E161" s="7" t="n">
         <v>46290.6875</v>
       </c>
-      <c r="F161" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F161" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>1443563801169773</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5920,9 +5920,14 @@
       <c r="E162" s="7" t="n">
         <v>46290.91666666666</v>
       </c>
-      <c r="F162" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F162" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>1085963987621650</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5953,9 +5953,14 @@
       <c r="E163" s="7" t="n">
         <v>46291.02083333334</v>
       </c>
-      <c r="F163" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F163" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>1575632120916868</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5986,9 +5986,14 @@
       <c r="E164" s="7" t="n">
         <v>46291.6875</v>
       </c>
-      <c r="F164" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F164" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>3745457745601891</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6019,9 +6019,14 @@
       <c r="E165" s="7" t="n">
         <v>46291.91666666666</v>
       </c>
-      <c r="F165" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F165" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>28480431651612306</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6052,9 +6052,14 @@
       <c r="E166" s="7" t="n">
         <v>46292.02083333334</v>
       </c>
-      <c r="F166" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F166" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>1107036678457864</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6085,9 +6085,14 @@
       <c r="E167" s="7" t="n">
         <v>46292.6875</v>
       </c>
-      <c r="F167" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F167" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>1413063304134069</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6118,9 +6118,14 @@
       <c r="E168" s="7" t="n">
         <v>46292.91666666666</v>
       </c>
-      <c r="F168" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F168" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>1789031958888014</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6151,9 +6151,14 @@
       <c r="E169" s="7" t="n">
         <v>46293.02083333334</v>
       </c>
-      <c r="F169" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F169" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>1766364778829124</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6184,9 +6184,14 @@
       <c r="E170" s="7" t="n">
         <v>46293.6875</v>
       </c>
-      <c r="F170" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F170" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>1123885289982391</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6217,9 +6217,14 @@
       <c r="E171" s="7" t="n">
         <v>46293.91666666666</v>
       </c>
-      <c r="F171" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F171" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>1983088969033034</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6250,9 +6250,14 @@
       <c r="E172" s="7" t="n">
         <v>46294.02083333334</v>
       </c>
-      <c r="F172" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F172" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>2912495095776942</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6283,9 +6283,14 @@
       <c r="E173" s="7" t="n">
         <v>46294.6875</v>
       </c>
-      <c r="F173" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F173" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>1027774243611067</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6316,9 +6316,14 @@
       <c r="E174" s="7" t="n">
         <v>46294.91666666666</v>
       </c>
-      <c r="F174" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F174" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>1610519607181795</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6349,9 +6349,14 @@
       <c r="E175" s="7" t="n">
         <v>46295.02083333334</v>
       </c>
-      <c r="F175" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F175" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>2012423576081801</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6382,9 +6382,14 @@
       <c r="E176" s="7" t="n">
         <v>46295.6875</v>
       </c>
-      <c r="F176" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F176" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>1116898111006622</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6415,9 +6415,14 @@
       <c r="E177" s="7" t="n">
         <v>46295.91666666666</v>
       </c>
-      <c r="F177" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F177" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>1125652750033124</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6448,9 +6448,14 @@
       <c r="E178" s="7" t="n">
         <v>46296.02083333334</v>
       </c>
-      <c r="F178" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F178" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>2165174500705092</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6481,9 +6481,14 @@
       <c r="E179" s="7" t="n">
         <v>46296.6875</v>
       </c>
-      <c r="F179" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F179" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>1027118100347838</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6514,9 +6514,14 @@
       <c r="E180" s="7" t="n">
         <v>46296.91666666666</v>
       </c>
-      <c r="F180" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F180" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>1085280044464850</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6547,9 +6547,14 @@
       <c r="E181" s="7" t="n">
         <v>46297.02083333334</v>
       </c>
-      <c r="F181" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F181" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>945188838187626</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6580,9 +6580,14 @@
       <c r="E182" s="7" t="n">
         <v>46297.6875</v>
       </c>
-      <c r="F182" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F182" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>1647937866942458</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6613,9 +6613,14 @@
       <c r="E183" s="7" t="n">
         <v>46297.91666666666</v>
       </c>
-      <c r="F183" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F183" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>1673779691125070</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6646,9 +6646,14 @@
       <c r="E184" s="7" t="n">
         <v>46298.02083333334</v>
       </c>
-      <c r="F184" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F184" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>1607056704218000</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6679,9 +6679,14 @@
       <c r="E185" s="7" t="n">
         <v>46298.6875</v>
       </c>
-      <c r="F185" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F185" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>1626219729207484</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6712,9 +6712,14 @@
       <c r="E186" s="7" t="n">
         <v>46298.91666666666</v>
       </c>
-      <c r="F186" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F186" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>1098355906249663</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6745,9 +6745,14 @@
       <c r="E187" s="7" t="n">
         <v>46299.02083333334</v>
       </c>
-      <c r="F187" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F187" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>2273728550137094</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6778,9 +6778,14 @@
       <c r="E188" s="7" t="n">
         <v>46299.6875</v>
       </c>
-      <c r="F188" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F188" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>901072676365583</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6811,9 +6811,14 @@
       <c r="E189" s="7" t="n">
         <v>46299.91666666666</v>
       </c>
-      <c r="F189" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F189" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>3725940977563094</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6844,9 +6844,14 @@
       <c r="E190" s="7" t="n">
         <v>46300.02083333334</v>
       </c>
-      <c r="F190" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F190" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>1904138087630867</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6877,9 +6877,14 @@
       <c r="E191" s="7" t="n">
         <v>46300.6875</v>
       </c>
-      <c r="F191" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F191" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>1091162017023729</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6910,9 +6910,14 @@
       <c r="E192" s="7" t="n">
         <v>46300.91666666666</v>
       </c>
-      <c r="F192" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F192" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>944620254928184</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6943,9 +6943,14 @@
       <c r="E193" s="7" t="n">
         <v>46301.02083333334</v>
       </c>
-      <c r="F193" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F193" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>1979359566312578</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6976,9 +6976,14 @@
       <c r="E194" s="7" t="n">
         <v>46301.6875</v>
       </c>
-      <c r="F194" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F194" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>1132288462654520</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7009,9 +7009,14 @@
       <c r="E195" s="7" t="n">
         <v>46301.91666666666</v>
       </c>
-      <c r="F195" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F195" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>1631156965018671</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7042,9 +7042,14 @@
       <c r="E196" s="7" t="n">
         <v>46302.02083333334</v>
       </c>
-      <c r="F196" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F196" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>1972507533730482</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7075,9 +7075,14 @@
       <c r="E197" s="7" t="n">
         <v>46302.6875</v>
       </c>
-      <c r="F197" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F197" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>1823578505728305</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7108,9 +7108,14 @@
       <c r="E198" s="7" t="n">
         <v>46302.91666666666</v>
       </c>
-      <c r="F198" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F198" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>1089433153702779</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7141,9 +7141,14 @@
       <c r="E199" s="7" t="n">
         <v>46303.02083333334</v>
       </c>
-      <c r="F199" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F199" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>1635104501667818</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7174,9 +7174,14 @@
       <c r="E200" s="7" t="n">
         <v>46303.6875</v>
       </c>
-      <c r="F200" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F200" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>1050084418032017</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7207,9 +7207,14 @@
       <c r="E201" s="7" t="n">
         <v>46303.91666666666</v>
       </c>
-      <c r="F201" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F201" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>1872753157436072</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7240,9 +7240,14 @@
       <c r="E202" s="7" t="n">
         <v>46304.02083333334</v>
       </c>
-      <c r="F202" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F202" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>1120560297190841</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7273,9 +7273,14 @@
       <c r="E203" s="7" t="n">
         <v>46304.6875</v>
       </c>
-      <c r="F203" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F203" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>28883321704620613</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7306,9 +7306,14 @@
       <c r="E204" s="7" t="n">
         <v>46304.91666666666</v>
       </c>
-      <c r="F204" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F204" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>1840077743700470</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7339,9 +7339,14 @@
       <c r="E205" s="7" t="n">
         <v>46305.02083333334</v>
       </c>
-      <c r="F205" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F205" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>28621184317544258</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7372,9 +7372,14 @@
       <c r="E206" s="7" t="n">
         <v>46305.6875</v>
       </c>
-      <c r="F206" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F206" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>1462760019249779</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7405,9 +7405,14 @@
       <c r="E207" s="7" t="n">
         <v>46305.91666666666</v>
       </c>
-      <c r="F207" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F207" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>4606464916257099</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7438,9 +7438,14 @@
       <c r="E208" s="7" t="n">
         <v>46306.02083333334</v>
       </c>
-      <c r="F208" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F208" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>1607409624354912</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7471,9 +7471,14 @@
       <c r="E209" s="7" t="n">
         <v>46306.6875</v>
       </c>
-      <c r="F209" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F209" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>1106982168494632</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7504,9 +7504,14 @@
       <c r="E210" s="7" t="n">
         <v>46306.91666666666</v>
       </c>
-      <c r="F210" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F210" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>1089080310602332</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7537,9 +7537,14 @@
       <c r="E211" s="7" t="n">
         <v>46307.02083333334</v>
       </c>
-      <c r="F211" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F211" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>4075821636058469</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7570,9 +7570,14 @@
       <c r="E212" s="7" t="n">
         <v>46307.6875</v>
       </c>
-      <c r="F212" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F212" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>1808289460494760</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7603,9 +7603,14 @@
       <c r="E213" s="7" t="n">
         <v>46307.91666666666</v>
       </c>
-      <c r="F213" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F213" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>1120454390423420</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7636,9 +7636,14 @@
       <c r="E214" s="7" t="n">
         <v>46308.02083333334</v>
       </c>
-      <c r="F214" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F214" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>29247016741557292</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7669,9 +7669,14 @@
       <c r="E215" s="7" t="n">
         <v>46308.6875</v>
       </c>
-      <c r="F215" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F215" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>1078736241884089</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7702,9 +7702,14 @@
       <c r="E216" s="7" t="n">
         <v>46308.91666666666</v>
       </c>
-      <c r="F216" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F216" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>909258598784370</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7735,9 +7735,14 @@
       <c r="E217" s="7" t="n">
         <v>46309.02083333334</v>
       </c>
-      <c r="F217" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F217" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>1124030129991258</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7768,9 +7768,14 @@
       <c r="E218" s="7" t="n">
         <v>46309.6875</v>
       </c>
-      <c r="F218" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F218" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>1125702583252457</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7801,9 +7801,14 @@
       <c r="E219" s="7" t="n">
         <v>46309.91666666666</v>
       </c>
-      <c r="F219" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F219" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>1340990721299097</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7834,9 +7834,14 @@
       <c r="E220" s="7" t="n">
         <v>46310.02083333334</v>
       </c>
-      <c r="F220" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F220" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>2622590758204517</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7867,9 +7867,14 @@
       <c r="E221" s="7" t="n">
         <v>46310.6875</v>
       </c>
-      <c r="F221" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F221" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>1109644518143705</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7900,9 +7900,14 @@
       <c r="E222" s="7" t="n">
         <v>46310.91666666666</v>
       </c>
-      <c r="F222" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F222" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>1101006446235645</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7933,9 +7933,14 @@
       <c r="E223" s="7" t="n">
         <v>46311.02083333334</v>
       </c>
-      <c r="F223" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F223" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>1086218097592336</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7966,9 +7966,14 @@
       <c r="E224" s="7" t="n">
         <v>46311.6875</v>
       </c>
-      <c r="F224" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F224" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>2346290509451405</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -7999,9 +7999,14 @@
       <c r="E225" s="7" t="n">
         <v>46311.91666666666</v>
       </c>
-      <c r="F225" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F225" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>4692370807659376</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8032,9 +8032,14 @@
       <c r="E226" s="7" t="n">
         <v>46312.02083333334</v>
       </c>
-      <c r="F226" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F226" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>29250211491269420</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8065,9 +8065,14 @@
       <c r="E227" s="7" t="n">
         <v>46312.6875</v>
       </c>
-      <c r="F227" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F227" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>1089649537180379</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8098,9 +8098,14 @@
       <c r="E228" s="7" t="n">
         <v>46312.91666666666</v>
       </c>
-      <c r="F228" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F228" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>1471235738406382</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8131,9 +8131,14 @@
       <c r="E229" s="7" t="n">
         <v>46313.02083333334</v>
       </c>
-      <c r="F229" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F229" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>1656361185906583</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8164,9 +8164,14 @@
       <c r="E230" s="7" t="n">
         <v>46313.6875</v>
       </c>
-      <c r="F230" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F230" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>1571683787981193</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8197,9 +8197,14 @@
       <c r="E231" s="7" t="n">
         <v>46313.91666666666</v>
       </c>
-      <c r="F231" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F231" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>1694603805507056</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8230,9 +8230,14 @@
       <c r="E232" s="7" t="n">
         <v>46314.02083333334</v>
       </c>
-      <c r="F232" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F232" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>2002220590427997</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8263,9 +8263,14 @@
       <c r="E233" s="7" t="n">
         <v>46314.6875</v>
       </c>
-      <c r="F233" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F233" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>1616067069974353</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8296,9 +8296,14 @@
       <c r="E234" s="7" t="n">
         <v>46314.91666666666</v>
       </c>
-      <c r="F234" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F234" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>1119688137217789</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8329,9 +8329,14 @@
       <c r="E235" s="7" t="n">
         <v>46315.02083333334</v>
       </c>
-      <c r="F235" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F235" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>1379139317366349</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8362,9 +8362,14 @@
       <c r="E236" s="7" t="n">
         <v>46315.6875</v>
       </c>
-      <c r="F236" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F236" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>1337843984960102</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8395,9 +8395,14 @@
       <c r="E237" s="7" t="n">
         <v>46315.91666666666</v>
       </c>
-      <c r="F237" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F237" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>2476265119565004</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8428,9 +8428,14 @@
       <c r="E238" s="7" t="n">
         <v>46316.02083333334</v>
       </c>
-      <c r="F238" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F238" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>1653623039794546</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8461,9 +8461,14 @@
       <c r="E239" s="7" t="n">
         <v>46316.6875</v>
       </c>
-      <c r="F239" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F239" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>2099410870946642</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8494,9 +8494,14 @@
       <c r="E240" s="7" t="n">
         <v>46316.91666666666</v>
       </c>
-      <c r="F240" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F240" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>1509876730970064</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8527,9 +8527,14 @@
       <c r="E241" s="7" t="n">
         <v>46317.02083333334</v>
       </c>
-      <c r="F241" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F241" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>1808350536852679</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8560,9 +8560,14 @@
       <c r="E242" s="7" t="n">
         <v>46317.6875</v>
       </c>
-      <c r="F242" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F242" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>2678782179302077</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8593,9 +8593,14 @@
       <c r="E243" s="7" t="n">
         <v>46317.91666666666</v>
       </c>
-      <c r="F243" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F243" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>1612663110603380</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8626,9 +8626,14 @@
       <c r="E244" s="7" t="n">
         <v>46318.02083333334</v>
       </c>
-      <c r="F244" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F244" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>1676078530619438</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8659,9 +8659,14 @@
       <c r="E245" s="7" t="n">
         <v>46318.6875</v>
       </c>
-      <c r="F245" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F245" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>2391165371687605</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8692,9 +8692,14 @@
       <c r="E246" s="7" t="n">
         <v>46318.91666666666</v>
       </c>
-      <c r="F246" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F246" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>1011938805268787</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8725,9 +8725,14 @@
       <c r="E247" s="7" t="n">
         <v>46319.02083333334</v>
       </c>
-      <c r="F247" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F247" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>1143158675332686</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8758,9 +8758,14 @@
       <c r="E248" s="7" t="n">
         <v>46319.6875</v>
       </c>
-      <c r="F248" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F248" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>1438622277671157</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8791,9 +8791,14 @@
       <c r="E249" s="7" t="n">
         <v>46319.91666666666</v>
       </c>
-      <c r="F249" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F249" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>1101285186020557</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8824,9 +8824,14 @@
       <c r="E250" s="7" t="n">
         <v>46320.02083333334</v>
       </c>
-      <c r="F250" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F250" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>1903201177691146</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8857,9 +8857,14 @@
       <c r="E251" s="7" t="n">
         <v>46320.6875</v>
       </c>
-      <c r="F251" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F251" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>1008907582237720</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8890,9 +8890,14 @@
       <c r="E252" s="7" t="n">
         <v>46320.91666666666</v>
       </c>
-      <c r="F252" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F252" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>4686691921612845</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8923,9 +8923,14 @@
       <c r="E253" s="7" t="n">
         <v>46321.02083333334</v>
       </c>
-      <c r="F253" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F253" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>1120301763747539</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8956,9 +8956,14 @@
       <c r="E254" s="7" t="n">
         <v>46321.6875</v>
       </c>
-      <c r="F254" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F254" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>2602915553455779</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8989,9 +8989,14 @@
       <c r="E255" s="7" t="n">
         <v>46321.91666666666</v>
       </c>
-      <c r="F255" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F255" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>1099085202872045</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -9022,9 +9022,14 @@
       <c r="E256" s="7" t="n">
         <v>46322.02083333334</v>
       </c>
-      <c r="F256" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F256" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>1539313571369384</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -9055,9 +9055,14 @@
       <c r="E257" s="7" t="n">
         <v>46322.6875</v>
       </c>
-      <c r="F257" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F257" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>984981467986562</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -9088,9 +9088,14 @@
       <c r="E258" s="7" t="n">
         <v>46322.91666666666</v>
       </c>
-      <c r="F258" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F258" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>2187049492229858</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -9121,9 +9121,14 @@
       <c r="E259" s="7" t="n">
         <v>46323.02083333334</v>
       </c>
-      <c r="F259" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F259" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>1655419386239381</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -9154,9 +9154,14 @@
       <c r="E260" s="7" t="n">
         <v>46323.6875</v>
       </c>
-      <c r="F260" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F260" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>1635617794892056</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -9187,9 +9187,14 @@
       <c r="E261" s="7" t="n">
         <v>46323.91666666666</v>
       </c>
-      <c r="F261" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F261" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>2043495399643002</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -9220,9 +9220,14 @@
       <c r="E262" s="7" t="n">
         <v>46324.02083333334</v>
       </c>
-      <c r="F262" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F262" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>1872959490803711</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -9253,9 +9253,14 @@
       <c r="E263" s="7" t="n">
         <v>46324.6875</v>
       </c>
-      <c r="F263" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F263" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>1353079646753024</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -9286,9 +9286,14 @@
       <c r="E264" s="7" t="n">
         <v>46324.91666666666</v>
       </c>
-      <c r="F264" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F264" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>974941451829696</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -9319,9 +9319,14 @@
       <c r="E265" s="7" t="n">
         <v>46325.02083333334</v>
       </c>
-      <c r="F265" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F265" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>1102122939449109</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -9352,9 +9352,14 @@
       <c r="E266" s="7" t="n">
         <v>46325.6875</v>
       </c>
-      <c r="F266" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F266" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>4686489454971512</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -9385,9 +9385,14 @@
       <c r="E267" s="7" t="n">
         <v>46325.91666666666</v>
       </c>
-      <c r="F267" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F267" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>1347089170717557</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -9418,9 +9418,14 @@
       <c r="E268" s="7" t="n">
         <v>46326.02083333334</v>
       </c>
-      <c r="F268" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F268" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>1848373909516093</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -9451,9 +9451,14 @@
       <c r="E269" s="7" t="n">
         <v>46326.6875</v>
       </c>
-      <c r="F269" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F269" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>2216733585570817</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -9484,9 +9484,14 @@
       <c r="E270" s="7" t="n">
         <v>46326.91666666666</v>
       </c>
-      <c r="F270" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F270" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>2482586578817552</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -9517,9 +9517,14 @@
       <c r="E271" s="7" t="n">
         <v>46327.02083333334</v>
       </c>
-      <c r="F271" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F271" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>1090740160622684</t>
         </is>
       </c>
     </row>
